--- a/data/trans_orig/P1416-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2007</t>
+          <t>Población con diagnóstico de alergias crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49190</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43622</t>
+          <t>43248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52465</t>
+          <t>50592</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83929</t>
+          <t>84238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424586</t>
+          <t>424128</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449367</t>
+          <t>449307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263058</t>
+          <t>263432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284571</t>
+          <t>285054</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696528</t>
+          <t>696219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>727992</t>
+          <t>729865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38467</t>
+          <t>39367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39730</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>68211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63099</t>
+          <t>64549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97634</t>
+          <t>97805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328467</t>
+          <t>327567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348351</t>
+          <t>348126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>305091</t>
+          <t>303654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332135</t>
+          <t>332548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>641165</t>
+          <t>640994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675700</t>
+          <t>674250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>54392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38904</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66256</t>
+          <t>67088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>488245</t>
+          <t>487997</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512055</t>
+          <t>513443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151174</t>
+          <t>150250</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162677</t>
+          <t>162710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643915</t>
+          <t>643083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>671267</t>
+          <t>672186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58248</t>
+          <t>58363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92743</t>
+          <t>92905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57348</t>
+          <t>57255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>88864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124133</t>
+          <t>124331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170880</t>
+          <t>171013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1145591</t>
+          <t>1145429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1180086</t>
+          <t>1179971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625876</t>
+          <t>625421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>656937</t>
+          <t>657030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1781740</t>
+          <t>1781607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1828487</t>
+          <t>1828289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29484</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44598</t>
+          <t>45634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75423</t>
+          <t>77060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62691</t>
+          <t>64406</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96460</t>
+          <t>99788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>321071</t>
+          <t>320389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338843</t>
+          <t>337772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>493329</t>
+          <t>491692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>524154</t>
+          <t>523118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>822847</t>
+          <t>819519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>856616</t>
+          <t>854901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33915</t>
+          <t>32847</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81084</t>
+          <t>80370</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118895</t>
+          <t>117687</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100484</t>
+          <t>102326</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143830</t>
+          <t>144919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264286</t>
+          <t>265354</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282782</t>
+          <t>283885</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1129865</t>
+          <t>1131073</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1167676</t>
+          <t>1168390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1403130</t>
+          <t>1402041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1446476</t>
+          <t>1444634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>192021</t>
+          <t>190978</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>249286</t>
+          <t>248115</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>291966</t>
+          <t>291470</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>360481</t>
+          <t>360902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>501082</t>
+          <t>500184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>591495</t>
+          <t>590696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3020904</t>
+          <t>3022075</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3078169</t>
+          <t>3079212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3017643</t>
+          <t>3017222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3086158</t>
+          <t>3086654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6056819</t>
+          <t>6057618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6147232</t>
+          <t>6148130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2012</t>
+          <t>Población con diagnóstico de alergias crónicas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16214</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42892</t>
+          <t>44682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42652</t>
+          <t>43268</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70062</t>
+          <t>71901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401103</t>
+          <t>402560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420997</t>
+          <t>421598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271562</t>
+          <t>269772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292818</t>
+          <t>291993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681603</t>
+          <t>679764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>709013</t>
+          <t>708397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34762</t>
+          <t>34578</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49852</t>
+          <t>50919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45873</t>
+          <t>45038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77997</t>
+          <t>77882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384035</t>
+          <t>384219</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404351</t>
+          <t>404657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288159</t>
+          <t>287092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311795</t>
+          <t>310884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678811</t>
+          <t>678926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710935</t>
+          <t>711770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53437</t>
+          <t>51459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41544</t>
+          <t>41556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72668</t>
+          <t>71801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574956</t>
+          <t>576934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>602560</t>
+          <t>603760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231315</t>
+          <t>231187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248003</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>815854</t>
+          <t>816721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>846978</t>
+          <t>846966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40237</t>
+          <t>39314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71434</t>
+          <t>69035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51673</t>
+          <t>50954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83700</t>
+          <t>84923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100665</t>
+          <t>98919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143251</t>
+          <t>143947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1087575</t>
+          <t>1089974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1118772</t>
+          <t>1119695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682957</t>
+          <t>681734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>714984</t>
+          <t>715703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1782416</t>
+          <t>1781720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1825002</t>
+          <t>1826748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47212</t>
+          <t>48767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40996</t>
+          <t>41636</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71189</t>
+          <t>72369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478913</t>
+          <t>478787</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>497640</t>
+          <t>497680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>713034</t>
+          <t>711479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737281</t>
+          <t>735845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1199654</t>
+          <t>1198474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1229847</t>
+          <t>1229207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>30635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>56641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90269</t>
+          <t>88212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,47 +5133,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>90516</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>73554</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>112079</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>8,14%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>90516</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>72507</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>109399</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237411</t>
+          <t>236247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254987</t>
+          <t>254327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1019082</t>
+          <t>1021139</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1053377</t>
+          <t>1052710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,47 +5246,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>92,05%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1285717</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1264154</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1302679</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>93,42%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>91,86%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1285717</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1266834</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1303726</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>93,42%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>92,05%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152142</t>
+          <t>150909</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205479</t>
+          <t>201957</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230366</t>
+          <t>229479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>293567</t>
+          <t>292990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396911</t>
+          <t>392733</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>482929</t>
+          <t>478782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3215409</t>
+          <t>3218931</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3268746</t>
+          <t>3269979</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3255283</t>
+          <t>3255860</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3318484</t>
+          <t>3319371</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6486809</t>
+          <t>6490956</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6572827</t>
+          <t>6577005</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2016</t>
+          <t>Población con diagnóstico de alergias crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37075</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24618</t>
+          <t>24405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47290</t>
+          <t>47725</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46040</t>
+          <t>45808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77876</t>
+          <t>76244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392017</t>
+          <t>392081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412359</t>
+          <t>412556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299765</t>
+          <t>299330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322437</t>
+          <t>322650</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698271</t>
+          <t>699903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>730107</t>
+          <t>730339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32123</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>49894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44213</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72790</t>
+          <t>74869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345104</t>
+          <t>346322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364010</t>
+          <t>364426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322980</t>
+          <t>322379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>346098</t>
+          <t>345406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>676710</t>
+          <t>674631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705287</t>
+          <t>705745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34012</t>
+          <t>34737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>55221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>487902</t>
+          <t>487177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>507729</t>
+          <t>506861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138374</t>
+          <t>137947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154451</t>
+          <t>154496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632394</t>
+          <t>632815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>657624</t>
+          <t>656830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>29735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>54399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50982</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82559</t>
+          <t>81939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87834</t>
+          <t>87599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127799</t>
+          <t>126841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1095617</t>
+          <t>1095239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1119780</t>
+          <t>1119903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743317</t>
+          <t>743937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>774894</t>
+          <t>774984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1847715</t>
+          <t>1848673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1887680</t>
+          <t>1887915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40148</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>39204</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67772</t>
+          <t>68184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>63534</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96828</t>
+          <t>100886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>580558</t>
+          <t>580834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>601800</t>
+          <t>601858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>670472</t>
+          <t>670060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>698843</t>
+          <t>699040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1262122</t>
+          <t>1258064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1295523</t>
+          <t>1295416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41953</t>
+          <t>41602</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57027</t>
+          <t>57211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90609</t>
+          <t>93012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83008</t>
+          <t>82077</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>122956</t>
+          <t>121937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245192</t>
+          <t>245543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266493</t>
+          <t>266837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>991416</t>
+          <t>989013</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1024998</t>
+          <t>1024814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1246214</t>
+          <t>1247233</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1286162</t>
+          <t>1287093</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143971</t>
+          <t>144293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194588</t>
+          <t>196060</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>246023</t>
+          <t>247835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314578</t>
+          <t>313438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>407895</t>
+          <t>410801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>492199</t>
+          <t>490926</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3191134</t>
+          <t>3189662</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3241751</t>
+          <t>3241429</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3217018</t>
+          <t>3218158</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3285573</t>
+          <t>3283761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6425119</t>
+          <t>6426392</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6509423</t>
+          <t>6506517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2023</t>
+          <t>Población con diagnóstico de alergias crónicas en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33982</t>
+          <t>34933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65560</t>
+          <t>64047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56991</t>
+          <t>57053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83588</t>
+          <t>83944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98819</t>
+          <t>97939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138235</t>
+          <t>135794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438608</t>
+          <t>440121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470186</t>
+          <t>469235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>362086</t>
+          <t>361730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388683</t>
+          <t>388621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>811607</t>
+          <t>814048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>851023</t>
+          <t>851903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>33775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65033</t>
+          <t>64384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61423</t>
+          <t>62253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>78360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117657</t>
+          <t>114916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386222</t>
+          <t>386871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416572</t>
+          <t>417480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319750</t>
+          <t>318920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341413</t>
+          <t>341819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>714771</t>
+          <t>717512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752578</t>
+          <t>754068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86277</t>
+          <t>86407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28477</t>
+          <t>29602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109910</t>
+          <t>114153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>580192</t>
+          <t>580062</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651249</t>
+          <t>647124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136011</t>
+          <t>135467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149796</t>
+          <t>149892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>723168</t>
+          <t>718925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804601</t>
+          <t>803476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64710</t>
+          <t>64190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102726</t>
+          <t>103017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123414</t>
+          <t>119331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123153</t>
+          <t>122475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206122</t>
+          <t>207501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>932093</t>
+          <t>931802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>970109</t>
+          <t>970629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>849541</t>
+          <t>853624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>924491</t>
+          <t>927201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1801652</t>
+          <t>1800273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1884621</t>
+          <t>1885299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40112</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72835</t>
+          <t>71438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60847</t>
+          <t>59277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98742</t>
+          <t>97279</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107072</t>
+          <t>105619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160218</t>
+          <t>157216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401214</t>
+          <t>402611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>433937</t>
+          <t>435404</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>737358</t>
+          <t>738821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>775253</t>
+          <t>776823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1149931</t>
+          <t>1152933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1203077</t>
+          <t>1204530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65961</t>
+          <t>63921</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48624</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75874</t>
+          <t>76681</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78248</t>
+          <t>77511</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131033</t>
+          <t>128139</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173686</t>
+          <t>175726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218013</t>
+          <t>218663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>681430</t>
+          <t>680623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>708680</t>
+          <t>707161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>865918</t>
+          <t>868812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>918703</t>
+          <t>919440</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>250905</t>
+          <t>247471</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>368615</t>
+          <t>373494</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,82 +10711,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>375094</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>305202</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>418763</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>693829</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>597327</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>757948</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>10,94%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>375094</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>305638</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>414865</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>693829</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>601377</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>762272</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3001792</t>
+          <t>2996913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3119502</t>
+          <t>3122936</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,82 +10824,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4621</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3184721</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3141052</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3254613</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>89,46%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>7620</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6236393</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6172274</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6332895</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>89,06%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4621</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3184721</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3144950</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3254177</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>89,46%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>88,35%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>7620</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6236393</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6167950</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6328845</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1416-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49648</t>
+          <t>48360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21626</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43248</t>
+          <t>43927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>52353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84238</t>
+          <t>84553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424128</t>
+          <t>425416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449307</t>
+          <t>450010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263432</t>
+          <t>262753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285054</t>
+          <t>285264</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696219</t>
+          <t>695904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>729865</t>
+          <t>728104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39367</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68211</t>
+          <t>67186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64549</t>
+          <t>63642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97805</t>
+          <t>97863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>327567</t>
+          <t>327115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348126</t>
+          <t>348226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>304679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332548</t>
+          <t>332410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>640994</t>
+          <t>640936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674250</t>
+          <t>675157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>29372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54392</t>
+          <t>54597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>38275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67088</t>
+          <t>66756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>487997</t>
+          <t>487792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513443</t>
+          <t>513017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150250</t>
+          <t>149396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162710</t>
+          <t>162603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643083</t>
+          <t>643415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>672186</t>
+          <t>671896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58363</t>
+          <t>58740</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92905</t>
+          <t>91953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>57573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88864</t>
+          <t>88281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>122485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171013</t>
+          <t>169248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1145429</t>
+          <t>1146381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1179971</t>
+          <t>1179594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625421</t>
+          <t>626004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>657030</t>
+          <t>656712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1781607</t>
+          <t>1783372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1828289</t>
+          <t>1830135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30166</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +2120,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>60031</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>46887</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>75730</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>79175</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>63686</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>98972</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>8,61%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>60031</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>45634</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>77060</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>79175</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>64406</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>99788</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>320389</t>
+          <t>321776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337772</t>
+          <t>338551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +2233,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>91,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>508721</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>493022</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>521865</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>89,45%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>86,68%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>91,76%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>840132</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>820335</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>855621</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>91,39%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>508721</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>491692</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>523118</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,45%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>86,45%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>840132</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>819519</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>854901</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>91,39%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>33330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80370</t>
+          <t>81541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>118681</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102326</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144919</t>
+          <t>140870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265354</t>
+          <t>264871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283885</t>
+          <t>282931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1131073</t>
+          <t>1130079</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1168390</t>
+          <t>1167219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1402041</t>
+          <t>1406090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1444634</t>
+          <t>1446559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>190978</t>
+          <t>191040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>248115</t>
+          <t>248433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>291470</t>
+          <t>291623</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>360902</t>
+          <t>361410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>500184</t>
+          <t>497399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>590696</t>
+          <t>595713</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3022075</t>
+          <t>3021757</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3079212</t>
+          <t>3079150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3017222</t>
+          <t>3016714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3086654</t>
+          <t>3086501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6057618</t>
+          <t>6052601</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6148130</t>
+          <t>6150915</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44682</t>
+          <t>42524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43268</t>
+          <t>41506</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71901</t>
+          <t>71081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402560</t>
+          <t>402971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421598</t>
+          <t>420907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269772</t>
+          <t>271930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291993</t>
+          <t>293065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>679764</t>
+          <t>680584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708397</t>
+          <t>710159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34578</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50919</t>
+          <t>50307</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45038</t>
+          <t>45827</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77882</t>
+          <t>77280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384219</t>
+          <t>384330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404657</t>
+          <t>404739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287092</t>
+          <t>287704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>310884</t>
+          <t>311991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678926</t>
+          <t>679528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711770</t>
+          <t>710981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24633</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51459</t>
+          <t>51314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>29620</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41556</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71801</t>
+          <t>75382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>576934</t>
+          <t>577079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>603760</t>
+          <t>603722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231187</t>
+          <t>230509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>247461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>816721</t>
+          <t>813140</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>846966</t>
+          <t>846042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39314</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69035</t>
+          <t>69854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50954</t>
+          <t>50785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84923</t>
+          <t>85670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98919</t>
+          <t>99731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143947</t>
+          <t>143253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1089974</t>
+          <t>1089155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1119695</t>
+          <t>1118308</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>681734</t>
+          <t>680987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>715703</t>
+          <t>715872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1781720</t>
+          <t>1782414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1826748</t>
+          <t>1825936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>31024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41636</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72369</t>
+          <t>69239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478787</t>
+          <t>479572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>497680</t>
+          <t>498882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711479</t>
+          <t>711839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>735845</t>
+          <t>735526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1198474</t>
+          <t>1201604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1229207</t>
+          <t>1231130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56641</t>
+          <t>54802</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88212</t>
+          <t>89839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73554</t>
+          <t>73267</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112079</t>
+          <t>110946</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236247</t>
+          <t>237499</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254327</t>
+          <t>255584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1021139</t>
+          <t>1019512</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1052710</t>
+          <t>1054549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1264154</t>
+          <t>1265287</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1302679</t>
+          <t>1302966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150909</t>
+          <t>149342</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201957</t>
+          <t>203834</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>229479</t>
+          <t>227139</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>292990</t>
+          <t>291113</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>392733</t>
+          <t>397514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>478782</t>
+          <t>477824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3218931</t>
+          <t>3217054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3269979</t>
+          <t>3271546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3255860</t>
+          <t>3257737</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3319371</t>
+          <t>3321711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6490956</t>
+          <t>6491914</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6577005</t>
+          <t>6572224</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>38636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24405</t>
+          <t>24296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47725</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45808</t>
+          <t>45298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76244</t>
+          <t>77583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392081</t>
+          <t>390456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412556</t>
+          <t>412203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299330</t>
+          <t>300885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322650</t>
+          <t>322759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>699903</t>
+          <t>698564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>730339</t>
+          <t>730849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>31424</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49894</t>
+          <t>51379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43755</t>
+          <t>44049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74869</t>
+          <t>75251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346322</t>
+          <t>345803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364426</t>
+          <t>364686</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322379</t>
+          <t>320894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345406</t>
+          <t>344518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674631</t>
+          <t>674249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705745</t>
+          <t>705451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28176</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55221</t>
+          <t>56302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>487177</t>
+          <t>488331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506861</t>
+          <t>507693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137947</t>
+          <t>138396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154496</t>
+          <t>154763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632815</t>
+          <t>631734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656830</t>
+          <t>657605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>29358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54399</t>
+          <t>53747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50892</t>
+          <t>50359</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81939</t>
+          <t>83131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87599</t>
+          <t>86980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126841</t>
+          <t>128007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1095239</t>
+          <t>1095891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1119903</t>
+          <t>1120280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743937</t>
+          <t>742745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>774984</t>
+          <t>775517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848673</t>
+          <t>1847507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1887915</t>
+          <t>1888534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39872</t>
+          <t>42590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39204</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68184</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63534</t>
+          <t>64805</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100886</t>
+          <t>100917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>580834</t>
+          <t>578116</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>601858</t>
+          <t>600741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>670060</t>
+          <t>671119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>699040</t>
+          <t>699119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1258064</t>
+          <t>1258033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1295416</t>
+          <t>1294145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20308</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41602</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57211</t>
+          <t>56827</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93012</t>
+          <t>90926</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82077</t>
+          <t>83397</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121937</t>
+          <t>122736</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245543</t>
+          <t>246106</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266837</t>
+          <t>267516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>989013</t>
+          <t>991099</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1024814</t>
+          <t>1025198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1247233</t>
+          <t>1246434</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1287093</t>
+          <t>1285773</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144293</t>
+          <t>143948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196060</t>
+          <t>193786</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>247835</t>
+          <t>250141</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313438</t>
+          <t>315692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>410801</t>
+          <t>410250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>490926</t>
+          <t>491708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3189662</t>
+          <t>3191936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3241429</t>
+          <t>3241774</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3218158</t>
+          <t>3215904</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3283761</t>
+          <t>3281455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6426392</t>
+          <t>6425610</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6506517</t>
+          <t>6507068</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47589</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34933</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64047</t>
+          <t>69290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69581</t>
+          <t>76695</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57053</t>
+          <t>64175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83944</t>
+          <t>90652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>117170</t>
+          <t>128224</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97939</t>
+          <t>107244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135794</t>
+          <t>150580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>456579</t>
+          <t>497962</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440121</t>
+          <t>480201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469235</t>
+          <t>512158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>376093</t>
+          <t>409821</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>361730</t>
+          <t>395864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388621</t>
+          <t>422341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>832672</t>
+          <t>907783</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>814048</t>
+          <t>885427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>851903</t>
+          <t>928763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504168</t>
+          <t>549491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504168</t>
+          <t>549491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504168</t>
+          <t>549491</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445674</t>
+          <t>486516</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445674</t>
+          <t>486516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445674</t>
+          <t>486516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>949842</t>
+          <t>1036007</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>949842</t>
+          <t>1036007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949842</t>
+          <t>1036007</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46523</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>33572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64384</t>
+          <t>62084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50050</t>
+          <t>55821</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39354</t>
+          <t>45184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62253</t>
+          <t>69555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>96574</t>
+          <t>102553</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78360</t>
+          <t>84037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114916</t>
+          <t>122898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>404732</t>
+          <t>435544</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386871</t>
+          <t>420192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417480</t>
+          <t>448704</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>331123</t>
+          <t>365860</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318920</t>
+          <t>352126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341819</t>
+          <t>376497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>735854</t>
+          <t>801404</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>717512</t>
+          <t>781059</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754068</t>
+          <t>819920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451255</t>
+          <t>482276</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451255</t>
+          <t>482276</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451255</t>
+          <t>482276</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381173</t>
+          <t>421681</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381173</t>
+          <t>421681</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381173</t>
+          <t>421681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832428</t>
+          <t>903957</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832428</t>
+          <t>903957</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832428</t>
+          <t>903957</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>56836</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>41696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86407</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31142</t>
+          <t>34179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73572</t>
+          <t>82835</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29602</t>
+          <t>68310</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>100878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>616094</t>
+          <t>412809</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>580062</t>
+          <t>397992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647124</t>
+          <t>427949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>143412</t>
+          <t>161216</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135467</t>
+          <t>153036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149892</t>
+          <t>168337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>759506</t>
+          <t>574025</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>718925</t>
+          <t>555982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>803476</t>
+          <t>588550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166609</t>
+          <t>187215</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166609</t>
+          <t>187215</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166609</t>
+          <t>187215</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833078</t>
+          <t>656860</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833078</t>
+          <t>656860</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833078</t>
+          <t>656860</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82271</t>
+          <t>90258</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64190</t>
+          <t>70759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103017</t>
+          <t>111275</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90196</t>
+          <t>103605</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>87299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119331</t>
+          <t>121424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>172467</t>
+          <t>193863</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122475</t>
+          <t>166404</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207501</t>
+          <t>221745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>952548</t>
+          <t>1041585</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>931802</t>
+          <t>1020568</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>970629</t>
+          <t>1061084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>882759</t>
+          <t>752095</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>853624</t>
+          <t>734276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>927201</t>
+          <t>768401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1835307</t>
+          <t>1793680</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1800273</t>
+          <t>1765798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1885299</t>
+          <t>1821139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>972955</t>
+          <t>855700</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>972955</t>
+          <t>855700</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>972955</t>
+          <t>855700</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2007774</t>
+          <t>1987543</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2007774</t>
+          <t>1987543</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2007774</t>
+          <t>1987543</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>56570</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>41595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71438</t>
+          <t>74689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>80397</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59277</t>
+          <t>80737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97279</t>
+          <t>111331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>133481</t>
+          <t>151719</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105619</t>
+          <t>130287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157216</t>
+          <t>177349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>420965</t>
+          <t>510406</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402611</t>
+          <t>492287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>435404</t>
+          <t>525381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>755703</t>
+          <t>731958</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>738821</t>
+          <t>715776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>776823</t>
+          <t>746370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1176668</t>
+          <t>1242364</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1152933</t>
+          <t>1216734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1204530</t>
+          <t>1263796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>836100</t>
+          <t>827107</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>836100</t>
+          <t>827107</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>836100</t>
+          <t>827107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1310149</t>
+          <t>1394083</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1310149</t>
+          <t>1394083</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1310149</t>
+          <t>1394083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>33346</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63921</t>
+          <t>54931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61672</t>
+          <t>66663</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50143</t>
+          <t>52625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76681</t>
+          <t>82038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>100566</t>
+          <t>100009</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77511</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128139</t>
+          <t>124895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>200753</t>
+          <t>203070</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175726</t>
+          <t>181485</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218663</t>
+          <t>216844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>695632</t>
+          <t>773175</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>680623</t>
+          <t>757800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>707161</t>
+          <t>787213</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>896385</t>
+          <t>976245</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868812</t>
+          <t>951359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>919440</t>
+          <t>998252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>239647</t>
+          <t>236416</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239647</t>
+          <t>236416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239647</t>
+          <t>236416</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>757304</t>
+          <t>839838</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>757304</t>
+          <t>839838</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>757304</t>
+          <t>839838</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>996951</t>
+          <t>1076254</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>996951</t>
+          <t>1076254</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>996951</t>
+          <t>1076254</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>318736</t>
+          <t>335271</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>247471</t>
+          <t>298825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>373494</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>375094</t>
+          <t>423932</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>305202</t>
+          <t>389631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>418763</t>
+          <t>458027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>693829</t>
+          <t>759202</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>597327</t>
+          <t>710899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>757948</t>
+          <t>815158</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3051671</t>
+          <t>3101376</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2996913</t>
+          <t>3060848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3122936</t>
+          <t>3137822</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3184721</t>
+          <t>3194126</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3141052</t>
+          <t>3160031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3254613</t>
+          <t>3228427</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6236393</t>
+          <t>6295503</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6172274</t>
+          <t>6239547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6332895</t>
+          <t>6343806</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3370407</t>
+          <t>3436647</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3370407</t>
+          <t>3436647</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3370407</t>
+          <t>3436647</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3559815</t>
+          <t>3618058</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3559815</t>
+          <t>3618058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3559815</t>
+          <t>3618058</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6930222</t>
+          <t>7054705</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6930222</t>
+          <t>7054705</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6930222</t>
+          <t>7054705</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
